--- a/artfynd/A 171-2021 artfynd.xlsx
+++ b/artfynd/A 171-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 171-2021 artfynd.xlsx
+++ b/artfynd/A 171-2021 artfynd.xlsx
@@ -2697,7 +2697,7 @@
         <v>120976764</v>
       </c>
       <c r="B20" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>120976762</v>
       </c>
       <c r="B21" t="n">
-        <v>94474</v>
+        <v>94484</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>120976761</v>
       </c>
       <c r="B22" t="n">
-        <v>88018</v>
+        <v>88024</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>120976765</v>
       </c>
       <c r="B23" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 171-2021 artfynd.xlsx
+++ b/artfynd/A 171-2021 artfynd.xlsx
@@ -2694,7 +2694,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120976764</v>
+        <v>120976765</v>
       </c>
       <c r="B20" t="n">
         <v>90662</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>368902</v>
+        <v>368880</v>
       </c>
       <c r="R20" t="n">
-        <v>6746413</v>
+        <v>6746441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120976762</v>
+        <v>120976764</v>
       </c>
       <c r="B21" t="n">
-        <v>94484</v>
+        <v>90662</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>369145</v>
+        <v>368902</v>
       </c>
       <c r="R21" t="n">
-        <v>6746561</v>
+        <v>6746413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120976765</v>
+        <v>120976762</v>
       </c>
       <c r="B23" t="n">
-        <v>90662</v>
+        <v>94484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>368880</v>
+        <v>369145</v>
       </c>
       <c r="R23" t="n">
-        <v>6746441</v>
+        <v>6746561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 171-2021 artfynd.xlsx
+++ b/artfynd/A 171-2021 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120976765</v>
+        <v>120976764</v>
       </c>
       <c r="B20" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>368880</v>
+        <v>368902</v>
       </c>
       <c r="R20" t="n">
-        <v>6746441</v>
+        <v>6746413</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120976764</v>
+        <v>120976765</v>
       </c>
       <c r="B21" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>368902</v>
+        <v>368880</v>
       </c>
       <c r="R21" t="n">
-        <v>6746413</v>
+        <v>6746441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120976761</v>
+        <v>120976762</v>
       </c>
       <c r="B22" t="n">
-        <v>88024</v>
+        <v>94496</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,25 +2910,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>368866</v>
+        <v>369145</v>
       </c>
       <c r="R22" t="n">
-        <v>6746424</v>
+        <v>6746561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120976762</v>
+        <v>120976761</v>
       </c>
       <c r="B23" t="n">
-        <v>94484</v>
+        <v>88031</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3012,25 +3012,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>369145</v>
+        <v>368866</v>
       </c>
       <c r="R23" t="n">
-        <v>6746561</v>
+        <v>6746424</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
